--- a/Sitios MBB/Correcciones Json Sitios.xlsx
+++ b/Sitios MBB/Correcciones Json Sitios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69517450a5f14e94/Intranet/Sitios MBB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="542" documentId="8_{C5BAA5DA-583E-4BCA-9836-C3A43265B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C8AB19-F97A-420C-ADF0-C25C94778B86}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="8_{C5BAA5DA-583E-4BCA-9836-C3A43265B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D68E56-297C-42F1-8ECF-EAE1C807B914}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EF617B91-231F-446F-9C8D-9D09E3385D4E}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="433">
   <si>
     <t>BUSCAR</t>
   </si>
@@ -1261,6 +1260,84 @@
   </si>
   <si>
     <t>Amatlán de Cañas</t>
+  </si>
+  <si>
+    <t>Tepotzotl�n</t>
+  </si>
+  <si>
+    <t>Tepotzotlán</t>
+  </si>
+  <si>
+    <t>Huehuetán</t>
+  </si>
+  <si>
+    <t>Huehuet�n</t>
+  </si>
+  <si>
+    <t>Tl�huac</t>
+  </si>
+  <si>
+    <t>Tláhuac</t>
+  </si>
+  <si>
+    <t>Tuxtla Guti�rrez</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez</t>
+  </si>
+  <si>
+    <t>Atizap�n de Zaragoza</t>
+  </si>
+  <si>
+    <t>Atizapán de Zaragoza</t>
+  </si>
+  <si>
+    <t>Teotitl�n de Flores Mag�n</t>
+  </si>
+  <si>
+    <t>Teotitlán de Flores Magón</t>
+  </si>
+  <si>
+    <t>Teotihuacán</t>
+  </si>
+  <si>
+    <t>Teotihuac�n</t>
+  </si>
+  <si>
+    <t>San Jos� Independencia</t>
+  </si>
+  <si>
+    <t>San José Independencia</t>
+  </si>
+  <si>
+    <t>San Crist�bal de las Casas</t>
+  </si>
+  <si>
+    <t>San Cristóbal de las Casas</t>
+  </si>
+  <si>
+    <t>Tecpat�n</t>
+  </si>
+  <si>
+    <t>Tecpatán</t>
+  </si>
+  <si>
+    <t>Chil�n</t>
+  </si>
+  <si>
+    <t>Chilón</t>
+  </si>
+  <si>
+    <t>San Sebasti�n Tlacotepec</t>
+  </si>
+  <si>
+    <t>San Sebastián Tlacotepec</t>
+  </si>
+  <si>
+    <t>General Francisco R. Murgu�a</t>
+  </si>
+  <si>
+    <t>General Francisco R. Murguía</t>
   </si>
 </sst>
 </file>
@@ -1716,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A7AFB2-C9AD-4CFE-B0B7-3A4601322FD3}">
-  <dimension ref="A1:C206"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" style="4" customWidth="1"/>
@@ -3392,15 +3469,119 @@
       </c>
       <c r="C206" s="4"/>
     </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A188:A194">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B13 B16:B111 B117:B187">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C188:C194">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A188:A194">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
